--- a/ci-cd-merge-resolver/repoCollector/datasets/dependency-track.xlsx
+++ b/ci-cd-merge-resolver/repoCollector/datasets/dependency-track.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="22" uniqueCount="22">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="19" uniqueCount="19">
   <si>
     <t>mergeCommit</t>
   </si>
@@ -44,6 +44,24 @@
     <t>isMultiModule</t>
   </si>
   <si>
+    <t>5d2606ffeb41fa7f5690d0bfd4dcc7a0b6783e19</t>
+  </si>
+  <si>
+    <t>ac449d31142ab5903bfe68d0b02d832f1179a518</t>
+  </si>
+  <si>
+    <t>a77f787a8e90249b7046cba5752e3a00fd034796</t>
+  </si>
+  <si>
+    <t>2ebca5d79ab71ae76bdb344cc9b6b13c5512984a</t>
+  </si>
+  <si>
+    <t>ea2276d7779e7a2d37d05dd3917e5fa85968bfbc</t>
+  </si>
+  <si>
+    <t>0baecf6b70810aceeb1eccb15cc15de34de52fb2</t>
+  </si>
+  <si>
     <t>d1753a68ec899ca5212977d3195f238cb64f7ffc</t>
   </si>
   <si>
@@ -51,33 +69,6 @@
   </si>
   <si>
     <t>16070401a061158543fa2dafaa7c41d7cb556358</t>
-  </si>
-  <si>
-    <t>380107d92861d6f8f851b1406ce06f72064c9a2e</t>
-  </si>
-  <si>
-    <t>f14fc9a005743f74b5a8ae5812792eac3b956cc5</t>
-  </si>
-  <si>
-    <t>69cd5401d0bfaba0d19d08ea4025e226e6f66a65</t>
-  </si>
-  <si>
-    <t>5d2606ffeb41fa7f5690d0bfd4dcc7a0b6783e19</t>
-  </si>
-  <si>
-    <t>ac449d31142ab5903bfe68d0b02d832f1179a518</t>
-  </si>
-  <si>
-    <t>a77f787a8e90249b7046cba5752e3a00fd034796</t>
-  </si>
-  <si>
-    <t>2ebca5d79ab71ae76bdb344cc9b6b13c5512984a</t>
-  </si>
-  <si>
-    <t>ea2276d7779e7a2d37d05dd3917e5fa85968bfbc</t>
-  </si>
-  <si>
-    <t>0baecf6b70810aceeb1eccb15cc15de34de52fb2</t>
   </si>
 </sst>
 </file>
@@ -122,7 +113,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:J5"/>
+  <dimension ref="A1:J4"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <sheetData>
     <row r="1">
@@ -168,10 +159,10 @@
         <v>12</v>
       </c>
       <c r="D2" t="n" s="0">
-        <v>445.0</v>
+        <v>851.0</v>
       </c>
       <c r="E2" t="n" s="0">
-        <v>1.0</v>
+        <v>2.0</v>
       </c>
       <c r="F2" t="n" s="0">
         <v>1.0</v>
@@ -183,7 +174,7 @@
         <v>1</v>
       </c>
       <c r="I2" t="n" s="0">
-        <v>93.19400787353516</v>
+        <v>466.0479431152344</v>
       </c>
       <c r="J2" t="b" s="0">
         <v>0</v>
@@ -200,13 +191,13 @@
         <v>15</v>
       </c>
       <c r="D3" t="n" s="0">
-        <v>485.0</v>
+        <v>862.0</v>
       </c>
       <c r="E3" t="n" s="0">
-        <v>3.0</v>
+        <v>1.0</v>
       </c>
       <c r="F3" t="n" s="0">
-        <v>3.0</v>
+        <v>1.0</v>
       </c>
       <c r="G3" t="b" s="0">
         <v>0</v>
@@ -215,7 +206,7 @@
         <v>1</v>
       </c>
       <c r="I3" t="n" s="0">
-        <v>135.19398498535156</v>
+        <v>623.4322509765625</v>
       </c>
       <c r="J3" t="b" s="0">
         <v>0</v>
@@ -232,10 +223,10 @@
         <v>18</v>
       </c>
       <c r="D4" t="n" s="0">
-        <v>424.0</v>
+        <v>2676.0</v>
       </c>
       <c r="E4" t="n" s="0">
-        <v>2.0</v>
+        <v>1.0</v>
       </c>
       <c r="F4" t="n" s="0">
         <v>1.0</v>
@@ -247,41 +238,9 @@
         <v>1</v>
       </c>
       <c r="I4" t="n" s="0">
-        <v>397.0420227050781</v>
+        <v>266.4270324707031</v>
       </c>
       <c r="J4" t="b" s="0">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="s" s="0">
-        <v>19</v>
-      </c>
-      <c r="B5" t="s" s="0">
-        <v>20</v>
-      </c>
-      <c r="C5" t="s" s="0">
-        <v>21</v>
-      </c>
-      <c r="D5" t="n" s="0">
-        <v>510.0</v>
-      </c>
-      <c r="E5" t="n" s="0">
-        <v>1.0</v>
-      </c>
-      <c r="F5" t="n" s="0">
-        <v>1.0</v>
-      </c>
-      <c r="G5" t="b" s="0">
-        <v>0</v>
-      </c>
-      <c r="H5" t="b" s="0">
-        <v>1</v>
-      </c>
-      <c r="I5" t="n" s="0">
-        <v>583.18603515625</v>
-      </c>
-      <c r="J5" t="b" s="0">
         <v>0</v>
       </c>
     </row>
